--- a/samples/corpus/full/entreprise/equipment-register/2026-04-10_registre-du-materiel.xlsx
+++ b/samples/corpus/full/entreprise/equipment-register/2026-04-10_registre-du-materiel.xlsx
@@ -539,14 +539,8 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>VGP annuelle (12 mois)</t>
-        </is>
-      </c>
-      <c r="F3" s="3" t="n">
-        <v>45979</v>
-      </c>
-      <c r="G3" s="3" t="n">
-        <v>46344</v>
+          <t>Non soumis à VGP (jamais utilisée en levage)</t>
+        </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
